--- a/stories/arbres/TREE-FAM-015.xlsx
+++ b/stories/arbres/TREE-FAM-015.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le soir, Maya est à la maison. Un petit bruit arrive. Maya a peur. Son ventre se serre. Maman dit : ce qui fait peur se raconte. On va raconter à papa ou maman. Maya hoche la tête.</t>
+          <t>Le soir, Maya est à la maison. Un petit bruit arrive. Maya a peur. Son ventre se serre. Ce qui fait peur se raconte. On va raconter à papa ou maman. Maya hoche la tête.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Maya est à la maison. Un petit bruit arrive. Maya a peur. Son ventre se serre.
+maman|Ce qui fait peur se raconte. On va raconter à papa ou maman.
+narrateur|Maya hoche la tête.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le couloir, la chambre, ou le jardin la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1540,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Dans le couloir, Maya a peur. Elle va raconter à papa ou maman. Elle dit : j'ai peur.</t>
+          <t>Dans le couloir, Maya a peur. Elle va raconter à papa ou maman. J'ai peur.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1678,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Dans le couloir, Maya a peur. Elle va raconter à papa ou maman.
+narrateur|J'ai peur.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1864,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Dans le couloir, Maya a peur. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2037,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a eu peur. Elle a raconté à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2228,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un bruit, un manteau, ou une ombre.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2395,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Un bruit dans le couloir. Maya a peur. Elle raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2586,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou les deux.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2753,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint maman. Elle a eu peur de un bruit, à le couloir. Elle a raconté à papa ou maman. Ils écoutent.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2920,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3087,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint papa. Elle a eu peur de un bruit, à le couloir. Elle a raconté à papa ou maman. Ils écoutent.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3254,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3421,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint les deux. Elle a eu peur de un bruit, à le couloir. Elle a raconté à papa ou maman. Ils écoutent.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3588,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3755,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Le manteau bouge. Maya a peur. Elle raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3946,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou les deux.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4013,6 +4113,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint maman. Elle a eu peur de un manteau, à le couloir. Elle a raconté à papa ou maman. Ils écoutent.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4280,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4447,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint papa. Elle a eu peur de un manteau, à le couloir. Elle a raconté à papa ou maman. Ils écoutent.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4614,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4661,6 +4781,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint les deux. Elle a eu peur de un manteau, à le couloir. Elle a raconté à papa ou maman. Ils écoutent.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4948,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5115,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Une ombre sur le mur. Maya a peur. Elle raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5306,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou les deux.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5473,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint maman. Elle a eu peur de une ombre, à le couloir. Elle a raconté à papa ou maman. Ils écoutent.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5640,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5807,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint papa. Elle a eu peur de une ombre, à le couloir. Elle a raconté à papa ou maman. Ils écoutent.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5974,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6141,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint les deux. Elle a eu peur de une ombre, à le couloir. Elle a raconté à papa ou maman. Ils écoutent.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6308,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6305,6 +6475,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Dans la chambre, Maya a peur. Elle raconte à papa ou maman. Le ventre est serré.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6485,6 +6660,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Dans la chambre, Maya a peur. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -6653,6 +6833,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. La peur se raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6841,6 +7026,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un bruit, un manteau, ou une ombre.</t>
         </is>
       </c>
     </row>
@@ -7005,6 +7195,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Un bruit dans la chambre. Maya a peur. Elle raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7191,6 +7386,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou les deux.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7353,6 +7553,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint maman. Elle a eu peur de un bruit, à la chambre. Elle a raconté à papa ou maman. Ils écoutent.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7515,6 +7720,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7677,6 +7887,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint papa. Elle a eu peur de un bruit, à la chambre. Elle a raconté à papa ou maman. Ils écoutent.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7839,6 +8054,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8001,6 +8221,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint les deux. Elle a eu peur de un bruit, à la chambre. Elle a raconté à papa ou maman. Ils écoutent.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8163,6 +8388,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8325,6 +8555,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Le manteau sur la chaise. Maya a peur. Elle raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8511,6 +8746,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou les deux.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8673,6 +8913,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint maman. Elle a eu peur de un manteau, à la chambre. Elle a raconté à papa ou maman. Ils écoutent.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8835,6 +9080,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8997,6 +9247,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint papa. Elle a eu peur de un manteau, à la chambre. Elle a raconté à papa ou maman. Ils écoutent.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9159,6 +9414,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9321,6 +9581,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint les deux. Elle a eu peur de un manteau, à la chambre. Elle a raconté à papa ou maman. Ils écoutent.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9483,6 +9748,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9645,6 +9915,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Une ombre près du lit. Maya a peur. Elle raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9831,6 +10106,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou les deux.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9993,6 +10273,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint maman. Elle a eu peur de une ombre, à la chambre. Elle a raconté à papa ou maman. Ils écoutent.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10155,6 +10440,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10317,6 +10607,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint papa. Elle a eu peur de une ombre, à la chambre. Elle a raconté à papa ou maman. Ils écoutent.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10479,6 +10774,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10641,6 +10941,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint les deux. Elle a eu peur de une ombre, à la chambre. Elle a raconté à papa ou maman. Ils écoutent.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10803,6 +11108,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10965,6 +11275,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Au jardin la nuit, Maya a peur. Elle rentre. Elle raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11145,6 +11460,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Au jardin, Maya a peur. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -11313,6 +11633,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a su raconter. Papa et maman écoutent.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11501,6 +11826,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre un bruit, un manteau, ou une ombre.</t>
         </is>
       </c>
     </row>
@@ -11665,6 +11995,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Un bruit au jardin. Maya a peur. Elle raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11851,6 +12186,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou les deux.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12013,6 +12353,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint maman. Elle a eu peur de un bruit, à le jardin la nuit. Elle a raconté à papa ou maman. Ils écoutent.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12175,6 +12520,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12337,6 +12687,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint papa. Elle a eu peur de un bruit, à le jardin la nuit. Elle a raconté à papa ou maman. Ils écoutent.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12499,6 +12854,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12661,6 +13021,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint les deux. Elle a eu peur de un bruit, à le jardin la nuit. Elle a raconté à papa ou maman. Ils écoutent.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12823,6 +13188,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12985,6 +13355,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Le manteau sur le banc. Maya a peur. Elle raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13171,6 +13546,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou les deux.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13333,6 +13713,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint maman. Elle a eu peur de un manteau, à le jardin la nuit. Elle a raconté à papa ou maman. Ils écoutent.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13495,6 +13880,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13657,6 +14047,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint papa. Elle a eu peur de un manteau, à le jardin la nuit. Elle a raconté à papa ou maman. Ils écoutent.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13819,6 +14214,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13981,6 +14381,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint les deux. Elle a eu peur de un manteau, à le jardin la nuit. Elle a raconté à papa ou maman. Ils écoutent.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14143,6 +14548,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14305,6 +14715,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Une ombre sous le pommier. Maya a peur. Elle raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14491,6 +14906,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre maman, papa, ou les deux.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14653,6 +15073,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint maman. Elle a eu peur de une ombre, à le jardin la nuit. Elle a raconté à papa ou maman. Ils écoutent.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14815,6 +15240,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14977,6 +15407,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint papa. Elle a eu peur de une ombre, à le jardin la nuit. Elle a raconté à papa ou maman. Ils écoutent.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15139,6 +15574,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15301,6 +15741,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Maya rejoint les deux. Elle a eu peur de une ombre, à le jardin la nuit. Elle a raconté à papa ou maman. Ils écoutent.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15463,6 +15908,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15481,7 +15931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15505,6 +15955,13 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-FAM-015.xlsx
+++ b/stories/arbres/TREE-FAM-015.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Maya hoche la tête.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1516,6 +1522,7 @@
           <t>narrateur|On peut prendre le couloir, la chambre, ou le jardin la nuit.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1684,6 +1691,7 @@
 narrateur|J'ai peur.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1871,6 +1879,7 @@
           <t>narrateur|Dans le couloir, Maya a peur. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2042,6 +2051,7 @@
           <t>narrateur|Maya a eu peur. Elle a raconté à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2233,6 +2243,7 @@
           <t>narrateur|On peut prendre un bruit, un manteau, ou une ombre.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2400,6 +2411,7 @@
           <t>narrateur|Un bruit dans le couloir. Maya a peur. Elle raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2591,6 +2603,7 @@
           <t>narrateur|On peut prendre maman, papa, ou les deux.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2758,6 +2771,7 @@
           <t>narrateur|Maya rejoint maman. Elle a eu peur de un bruit, à le couloir. Elle a raconté à papa ou maman. Ils écoutent.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2925,6 +2939,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3092,6 +3107,7 @@
           <t>narrateur|Maya rejoint papa. Elle a eu peur de un bruit, à le couloir. Elle a raconté à papa ou maman. Ils écoutent.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3259,6 +3275,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3426,6 +3443,7 @@
           <t>narrateur|Maya rejoint les deux. Elle a eu peur de un bruit, à le couloir. Elle a raconté à papa ou maman. Ils écoutent.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3593,6 +3611,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3760,6 +3779,7 @@
           <t>narrateur|Le manteau bouge. Maya a peur. Elle raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3951,6 +3971,7 @@
           <t>narrateur|On peut prendre maman, papa, ou les deux.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4118,6 +4139,7 @@
           <t>narrateur|Maya rejoint maman. Elle a eu peur de un manteau, à le couloir. Elle a raconté à papa ou maman. Ils écoutent.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4285,6 +4307,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4452,6 +4475,7 @@
           <t>narrateur|Maya rejoint papa. Elle a eu peur de un manteau, à le couloir. Elle a raconté à papa ou maman. Ils écoutent.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4619,6 +4643,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4786,6 +4811,7 @@
           <t>narrateur|Maya rejoint les deux. Elle a eu peur de un manteau, à le couloir. Elle a raconté à papa ou maman. Ils écoutent.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4953,6 +4979,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5120,6 +5147,7 @@
           <t>narrateur|Une ombre sur le mur. Maya a peur. Elle raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5311,6 +5339,7 @@
           <t>narrateur|On peut prendre maman, papa, ou les deux.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5478,6 +5507,7 @@
           <t>narrateur|Maya rejoint maman. Elle a eu peur de une ombre, à le couloir. Elle a raconté à papa ou maman. Ils écoutent.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5645,6 +5675,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5812,6 +5843,7 @@
           <t>narrateur|Maya rejoint papa. Elle a eu peur de une ombre, à le couloir. Elle a raconté à papa ou maman. Ils écoutent.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5979,6 +6011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6146,6 +6179,7 @@
           <t>narrateur|Maya rejoint les deux. Elle a eu peur de une ombre, à le couloir. Elle a raconté à papa ou maman. Ils écoutent.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6313,6 +6347,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6480,6 +6515,7 @@
           <t>narrateur|Dans la chambre, Maya a peur. Elle raconte à papa ou maman. Le ventre est serré.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6667,6 +6703,7 @@
           <t>narrateur|Dans la chambre, Maya a peur. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6838,6 +6875,7 @@
           <t>narrateur|Oui. La peur se raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7033,6 +7071,7 @@
           <t>narrateur|On peut prendre un bruit, un manteau, ou une ombre.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7200,6 +7239,7 @@
           <t>narrateur|Un bruit dans la chambre. Maya a peur. Elle raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7391,6 +7431,7 @@
           <t>narrateur|On peut prendre maman, papa, ou les deux.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7558,6 +7599,7 @@
           <t>narrateur|Maya rejoint maman. Elle a eu peur de un bruit, à la chambre. Elle a raconté à papa ou maman. Ils écoutent.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7725,6 +7767,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7892,6 +7935,7 @@
           <t>narrateur|Maya rejoint papa. Elle a eu peur de un bruit, à la chambre. Elle a raconté à papa ou maman. Ils écoutent.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8059,6 +8103,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8226,6 +8271,7 @@
           <t>narrateur|Maya rejoint les deux. Elle a eu peur de un bruit, à la chambre. Elle a raconté à papa ou maman. Ils écoutent.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8393,6 +8439,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8560,6 +8607,7 @@
           <t>narrateur|Le manteau sur la chaise. Maya a peur. Elle raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8751,6 +8799,7 @@
           <t>narrateur|On peut prendre maman, papa, ou les deux.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8918,6 +8967,7 @@
           <t>narrateur|Maya rejoint maman. Elle a eu peur de un manteau, à la chambre. Elle a raconté à papa ou maman. Ils écoutent.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9085,6 +9135,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9252,6 +9303,7 @@
           <t>narrateur|Maya rejoint papa. Elle a eu peur de un manteau, à la chambre. Elle a raconté à papa ou maman. Ils écoutent.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9419,6 +9471,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9586,6 +9639,7 @@
           <t>narrateur|Maya rejoint les deux. Elle a eu peur de un manteau, à la chambre. Elle a raconté à papa ou maman. Ils écoutent.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9753,6 +9807,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9920,6 +9975,7 @@
           <t>narrateur|Une ombre près du lit. Maya a peur. Elle raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10111,6 +10167,7 @@
           <t>narrateur|On peut prendre maman, papa, ou les deux.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10278,6 +10335,7 @@
           <t>narrateur|Maya rejoint maman. Elle a eu peur de une ombre, à la chambre. Elle a raconté à papa ou maman. Ils écoutent.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10445,6 +10503,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10612,6 +10671,7 @@
           <t>narrateur|Maya rejoint papa. Elle a eu peur de une ombre, à la chambre. Elle a raconté à papa ou maman. Ils écoutent.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10779,6 +10839,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10946,6 +11007,7 @@
           <t>narrateur|Maya rejoint les deux. Elle a eu peur de une ombre, à la chambre. Elle a raconté à papa ou maman. Ils écoutent.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11113,6 +11175,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11280,6 +11343,7 @@
           <t>narrateur|Au jardin la nuit, Maya a peur. Elle rentre. Elle raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11467,6 +11531,7 @@
           <t>narrateur|Au jardin, Maya a peur. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11638,6 +11703,7 @@
           <t>narrateur|Maya a su raconter. Papa et maman écoutent.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11833,6 +11899,7 @@
           <t>narrateur|On peut prendre un bruit, un manteau, ou une ombre.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12000,6 +12067,7 @@
           <t>narrateur|Un bruit au jardin. Maya a peur. Elle raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12191,6 +12259,7 @@
           <t>narrateur|On peut prendre maman, papa, ou les deux.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12358,6 +12427,7 @@
           <t>narrateur|Maya rejoint maman. Elle a eu peur de un bruit, à le jardin la nuit. Elle a raconté à papa ou maman. Ils écoutent.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12525,6 +12595,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12692,6 +12763,7 @@
           <t>narrateur|Maya rejoint papa. Elle a eu peur de un bruit, à le jardin la nuit. Elle a raconté à papa ou maman. Ils écoutent.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12859,6 +12931,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13026,6 +13099,7 @@
           <t>narrateur|Maya rejoint les deux. Elle a eu peur de un bruit, à le jardin la nuit. Elle a raconté à papa ou maman. Ils écoutent.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13193,6 +13267,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13360,6 +13435,7 @@
           <t>narrateur|Le manteau sur le banc. Maya a peur. Elle raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13551,6 +13627,7 @@
           <t>narrateur|On peut prendre maman, papa, ou les deux.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13718,6 +13795,7 @@
           <t>narrateur|Maya rejoint maman. Elle a eu peur de un manteau, à le jardin la nuit. Elle a raconté à papa ou maman. Ils écoutent.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13885,6 +13963,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14052,6 +14131,7 @@
           <t>narrateur|Maya rejoint papa. Elle a eu peur de un manteau, à le jardin la nuit. Elle a raconté à papa ou maman. Ils écoutent.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14219,6 +14299,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14386,6 +14467,7 @@
           <t>narrateur|Maya rejoint les deux. Elle a eu peur de un manteau, à le jardin la nuit. Elle a raconté à papa ou maman. Ils écoutent.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14553,6 +14635,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14720,6 +14803,7 @@
           <t>narrateur|Une ombre sous le pommier. Maya a peur. Elle raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14911,6 +14995,7 @@
           <t>narrateur|On peut prendre maman, papa, ou les deux.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15078,6 +15163,7 @@
           <t>narrateur|Maya rejoint maman. Elle a eu peur de une ombre, à le jardin la nuit. Elle a raconté à papa ou maman. Ils écoutent.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15245,6 +15331,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15412,6 +15499,7 @@
           <t>narrateur|Maya rejoint papa. Elle a eu peur de une ombre, à le jardin la nuit. Elle a raconté à papa ou maman. Ils écoutent.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15579,6 +15667,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15746,6 +15835,7 @@
           <t>narrateur|Maya rejoint les deux. Elle a eu peur de une ombre, à le jardin la nuit. Elle a raconté à papa ou maman. Ils écoutent.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15913,6 +16003,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15931,7 +16022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15962,6 +16053,20 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15976,7 +16081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16163,6 +16268,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
